--- a/research/traditional_assets/database/data/nigeria/nigeria_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_beverage_soft.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.208</v>
+        <v>-0.207</v>
       </c>
       <c r="G2">
-        <v>-0.543801652892562</v>
+        <v>-0.09906542056074766</v>
       </c>
       <c r="H2">
-        <v>-0.543801652892562</v>
+        <v>-0.09906542056074766</v>
       </c>
       <c r="I2">
-        <v>-0.6975206611570248</v>
+        <v>-0.3336448598130841</v>
       </c>
       <c r="J2">
-        <v>-0.6975206611570248</v>
+        <v>-0.3336448598130841</v>
       </c>
       <c r="K2">
-        <v>-0.852</v>
+        <v>-0.266</v>
       </c>
       <c r="L2">
-        <v>-0.7041322314049587</v>
+        <v>-0.2485981308411215</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.284</v>
+        <v>0.028</v>
       </c>
       <c r="V2">
-        <v>0.2448275862068965</v>
+        <v>0.02745098039215686</v>
       </c>
       <c r="W2">
-        <v>-0.2353591160220994</v>
+        <v>-0.1117647058823529</v>
       </c>
       <c r="X2">
-        <v>0.0937759006210865</v>
+        <v>0.1830803835837106</v>
       </c>
       <c r="Y2">
-        <v>-0.329135016643186</v>
+        <v>-0.2948450894660636</v>
       </c>
       <c r="Z2">
-        <v>0.33205268935236</v>
+        <v>0.4670449585333916</v>
       </c>
       <c r="AA2">
-        <v>-0.2316136114160263</v>
+        <v>-0.1558271497162811</v>
       </c>
       <c r="AB2">
-        <v>0.0926251082462607</v>
+        <v>0.1765176886121938</v>
       </c>
       <c r="AC2">
-        <v>-0.324238719662287</v>
+        <v>-0.3323448383284748</v>
       </c>
       <c r="AD2">
-        <v>0.035</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.035</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AG2">
-        <v>-0.249</v>
+        <v>0.05600000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.0292887029288703</v>
+        <v>0.07608695652173914</v>
       </c>
       <c r="AI2">
-        <v>0.01333333333333333</v>
+        <v>0.02697495183044316</v>
       </c>
       <c r="AJ2">
-        <v>-0.2733260153677278</v>
+        <v>0.05204460966542751</v>
       </c>
       <c r="AK2">
-        <v>-0.1063648013669372</v>
+        <v>0.01814646791963707</v>
       </c>
       <c r="AL2">
-        <v>0.006</v>
+        <v>0.016</v>
       </c>
       <c r="AM2">
-        <v>0.006</v>
+        <v>0.016</v>
       </c>
       <c r="AN2">
-        <v>-0.05319148936170213</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="AO2">
-        <v>-140.6666666666667</v>
+        <v>-22.3125</v>
       </c>
       <c r="AP2">
-        <v>0.3784194528875379</v>
+        <v>-0.2857142857142858</v>
       </c>
       <c r="AQ2">
-        <v>-140.6666666666667</v>
+        <v>-22.3125</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.208</v>
+        <v>-0.207</v>
       </c>
       <c r="G3">
-        <v>-0.543801652892562</v>
+        <v>-0.09906542056074766</v>
       </c>
       <c r="H3">
-        <v>-0.543801652892562</v>
+        <v>-0.09906542056074766</v>
       </c>
       <c r="I3">
-        <v>-0.6975206611570248</v>
+        <v>-0.3336448598130841</v>
       </c>
       <c r="J3">
-        <v>-0.6975206611570248</v>
+        <v>-0.3336448598130841</v>
       </c>
       <c r="K3">
-        <v>-0.852</v>
+        <v>-0.266</v>
       </c>
       <c r="L3">
-        <v>-0.7041322314049587</v>
+        <v>-0.2485981308411215</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.284</v>
+        <v>0.028</v>
       </c>
       <c r="V3">
-        <v>0.2448275862068965</v>
+        <v>0.02745098039215686</v>
       </c>
       <c r="W3">
-        <v>-0.2353591160220994</v>
+        <v>-0.1117647058823529</v>
       </c>
       <c r="X3">
-        <v>0.0937759006210865</v>
+        <v>0.1830803835837106</v>
       </c>
       <c r="Y3">
-        <v>-0.329135016643186</v>
+        <v>-0.2948450894660636</v>
       </c>
       <c r="Z3">
-        <v>0.33205268935236</v>
+        <v>0.4670449585333916</v>
       </c>
       <c r="AA3">
-        <v>-0.2316136114160263</v>
+        <v>-0.1558271497162811</v>
       </c>
       <c r="AB3">
-        <v>0.0926251082462607</v>
+        <v>0.1765176886121938</v>
       </c>
       <c r="AC3">
-        <v>-0.324238719662287</v>
+        <v>-0.3323448383284748</v>
       </c>
       <c r="AD3">
-        <v>0.035</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.035</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AG3">
-        <v>-0.249</v>
+        <v>0.05600000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.0292887029288703</v>
+        <v>0.07608695652173914</v>
       </c>
       <c r="AI3">
-        <v>0.01333333333333333</v>
+        <v>0.02697495183044316</v>
       </c>
       <c r="AJ3">
-        <v>-0.2733260153677278</v>
+        <v>0.05204460966542751</v>
       </c>
       <c r="AK3">
-        <v>-0.1063648013669372</v>
+        <v>0.01814646791963707</v>
       </c>
       <c r="AL3">
-        <v>0.006</v>
+        <v>0.016</v>
       </c>
       <c r="AM3">
-        <v>0.006</v>
+        <v>0.016</v>
       </c>
       <c r="AN3">
-        <v>-0.05319148936170213</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="AO3">
-        <v>-140.6666666666667</v>
+        <v>-22.3125</v>
       </c>
       <c r="AP3">
-        <v>0.3784194528875379</v>
+        <v>-0.2857142857142858</v>
       </c>
       <c r="AQ3">
-        <v>-140.6666666666667</v>
+        <v>-22.3125</v>
       </c>
     </row>
   </sheetData>
